--- a/data/CROSS/EXCLE/LUNR_1_20260921.xlsx
+++ b/data/CROSS/EXCLE/LUNR_1_20260921.xlsx
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
     </row>
     <row r="7">

--- a/data/CROSS/EXCLE/LUNR_1_20260921.xlsx
+++ b/data/CROSS/EXCLE/LUNR_1_20260921.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'30日跟踪'!$A$8</f>
+              <f>'30日跟踪'!$A$8:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'30日跟踪'!$D$8</f>
+              <f>'30日跟踪'!$D$8:$D$9</f>
             </numRef>
           </val>
         </ser>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
     </row>
     <row r="7">
@@ -708,6 +708,26 @@
       <c r="E8" t="inlineStr">
         <is>
           <t>第1/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B9" s="4" t="n">
+        <v>16.23999977111816</v>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>3.307884829875007</v>
+      </c>
+      <c r="D9" s="6">
+        <f>B9/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>第2/30个交易日</t>
         </is>
       </c>
     </row>

--- a/data/CROSS/EXCLE/LUNR_1_20260921.xlsx
+++ b/data/CROSS/EXCLE/LUNR_1_20260921.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'30日跟踪'!$A$8:$A$9</f>
+              <f>'30日跟踪'!$A$8:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'30日跟踪'!$D$8:$D$9</f>
+              <f>'30日跟踪'!$D$8:$D$11</f>
             </numRef>
           </val>
         </ser>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
     </row>
     <row r="7">
@@ -728,6 +728,46 @@
       <c r="E9" t="inlineStr">
         <is>
           <t>第2/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>15.23999977111816</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>-6.157635554764218</v>
+      </c>
+      <c r="D10" s="6">
+        <f>B10/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>第3/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>15.69999980926514</v>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>3.018372999051699</v>
+      </c>
+      <c r="D11" s="6">
+        <f>B11/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>第4/30个交易日</t>
         </is>
       </c>
     </row>

--- a/data/CROSS/EXCLE/LUNR_1_20260921.xlsx
+++ b/data/CROSS/EXCLE/LUNR_1_20260921.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'30日跟踪'!$A$8:$A$11</f>
+              <f>'30日跟踪'!$A$8:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'30日跟踪'!$D$8:$D$11</f>
+              <f>'30日跟踪'!$D$8:$D$12</f>
             </numRef>
           </val>
         </ser>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
     </row>
     <row r="7">
@@ -768,6 +768,26 @@
       <c r="E11" t="inlineStr">
         <is>
           <t>第4/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B12" s="4" t="n">
+        <v>15.60999965667725</v>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>-0.5732493865049482</v>
+      </c>
+      <c r="D12" s="6">
+        <f>B12/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>第5/30个交易日</t>
         </is>
       </c>
     </row>

--- a/data/CROSS/EXCLE/LUNR_1_20260921.xlsx
+++ b/data/CROSS/EXCLE/LUNR_1_20260921.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'30日跟踪'!$A$8:$A$12</f>
+              <f>'30日跟踪'!$A$8:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'30日跟踪'!$D$8:$D$12</f>
+              <f>'30日跟踪'!$D$8:$D$13</f>
             </numRef>
           </val>
         </ser>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46290</v>
+        <v>46293</v>
       </c>
     </row>
     <row r="7">
@@ -788,6 +788,26 @@
       <c r="E12" t="inlineStr">
         <is>
           <t>第5/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B13" s="4" t="n">
+        <v>15.19999980926514</v>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>-2.626520540868371</v>
+      </c>
+      <c r="D13" s="6">
+        <f>B13/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>第6/30个交易日</t>
         </is>
       </c>
     </row>

--- a/data/CROSS/EXCLE/LUNR_1_20260921.xlsx
+++ b/data/CROSS/EXCLE/LUNR_1_20260921.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'30日跟踪'!$A$8:$A$13</f>
+              <f>'30日跟踪'!$A$8:$A$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'30日跟踪'!$D$8:$D$13</f>
+              <f>'30日跟踪'!$D$8:$D$14</f>
             </numRef>
           </val>
         </ser>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
     </row>
     <row r="7">
@@ -808,6 +808,26 @@
       <c r="E13" t="inlineStr">
         <is>
           <t>第6/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B14" s="4" t="n">
+        <v>14.55000019073486</v>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>-4.276313333465087</v>
+      </c>
+      <c r="D14" s="6">
+        <f>B14/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>第7/30个交易日</t>
         </is>
       </c>
     </row>

--- a/data/CROSS/EXCLE/LUNR_1_20260921.xlsx
+++ b/data/CROSS/EXCLE/LUNR_1_20260921.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'30日跟踪'!$A$8:$A$14</f>
+              <f>'30日跟踪'!$A$8:$A$15</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'30日跟踪'!$D$8:$D$14</f>
+              <f>'30日跟踪'!$D$8:$D$15</f>
             </numRef>
           </val>
         </ser>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
     </row>
     <row r="7">
@@ -828,6 +828,26 @@
       <c r="E14" t="inlineStr">
         <is>
           <t>第7/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B15" s="4" t="n">
+        <v>14.23999977111816</v>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>-2.13058704847372</v>
+      </c>
+      <c r="D15" s="6">
+        <f>B15/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>第8/30个交易日</t>
         </is>
       </c>
     </row>

--- a/data/CROSS/EXCLE/LUNR_1_20260921.xlsx
+++ b/data/CROSS/EXCLE/LUNR_1_20260921.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'30日跟踪'!$A$8:$A$15</f>
+              <f>'30日跟踪'!$A$8:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'30日跟踪'!$D$8:$D$15</f>
+              <f>'30日跟踪'!$D$8:$D$16</f>
             </numRef>
           </val>
         </ser>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
     </row>
     <row r="7">
@@ -848,6 +848,26 @@
       <c r="E15" t="inlineStr">
         <is>
           <t>第8/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B16" s="4" t="n">
+        <v>14.05000019073486</v>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>-1.334266737620748</v>
+      </c>
+      <c r="D16" s="6">
+        <f>B16/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>第9/30个交易日</t>
         </is>
       </c>
     </row>

--- a/data/CROSS/EXCLE/LUNR_1_20260921.xlsx
+++ b/data/CROSS/EXCLE/LUNR_1_20260921.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'30日跟踪'!$A$8:$A$16</f>
+              <f>'30日跟踪'!$A$8:$A$17</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'30日跟踪'!$D$8:$D$16</f>
+              <f>'30日跟踪'!$D$8:$D$17</f>
             </numRef>
           </val>
         </ser>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
     </row>
     <row r="7">
@@ -868,6 +868,26 @@
       <c r="E16" t="inlineStr">
         <is>
           <t>第9/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B17" s="4" t="n">
+        <v>14.71000003814697</v>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>4.697507746991625</v>
+      </c>
+      <c r="D17" s="6">
+        <f>B17/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>第10/30个交易日</t>
         </is>
       </c>
     </row>

--- a/data/CROSS/EXCLE/LUNR_1_20260921.xlsx
+++ b/data/CROSS/EXCLE/LUNR_1_20260921.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'30日跟踪'!$A$8:$A$17</f>
+              <f>'30日跟踪'!$A$8:$A$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'30日跟踪'!$D$8:$D$17</f>
+              <f>'30日跟踪'!$D$8:$D$18</f>
             </numRef>
           </val>
         </ser>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46297</v>
+        <v>46300</v>
       </c>
     </row>
     <row r="7">
@@ -888,6 +888,26 @@
       <c r="E17" t="inlineStr">
         <is>
           <t>第10/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B18" s="4" t="n">
+        <v>14.28999996185303</v>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>-2.855201055097023</v>
+      </c>
+      <c r="D18" s="6">
+        <f>B18/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>第11/30个交易日</t>
         </is>
       </c>
     </row>

--- a/data/CROSS/EXCLE/LUNR_1_20260921.xlsx
+++ b/data/CROSS/EXCLE/LUNR_1_20260921.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'30日跟踪'!$A$8:$A$18</f>
+              <f>'30日跟踪'!$A$8:$A$19</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'30日跟踪'!$D$8:$D$18</f>
+              <f>'30日跟踪'!$D$8:$D$19</f>
             </numRef>
           </val>
         </ser>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
     </row>
     <row r="7">
@@ -908,6 +908,26 @@
       <c r="E18" t="inlineStr">
         <is>
           <t>第11/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B19" s="4" t="n">
+        <v>15.0600004196167</v>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>5.388386702723436</v>
+      </c>
+      <c r="D19" s="6">
+        <f>B19/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>第12/30个交易日</t>
         </is>
       </c>
     </row>

--- a/data/CROSS/EXCLE/LUNR_1_20260921.xlsx
+++ b/data/CROSS/EXCLE/LUNR_1_20260921.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'30日跟踪'!$A$8:$A$19</f>
+              <f>'30日跟踪'!$A$8:$A$20</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'30日跟踪'!$D$8:$D$19</f>
+              <f>'30日跟踪'!$D$8:$D$20</f>
             </numRef>
           </val>
         </ser>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="7">
@@ -928,6 +928,26 @@
       <c r="E19" t="inlineStr">
         <is>
           <t>第12/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B20" s="4" t="n">
+        <v>14.40999984741211</v>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>-4.316072736345467</v>
+      </c>
+      <c r="D20" s="6">
+        <f>B20/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>第13/30个交易日</t>
         </is>
       </c>
     </row>

--- a/data/CROSS/EXCLE/LUNR_1_20260921.xlsx
+++ b/data/CROSS/EXCLE/LUNR_1_20260921.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'30日跟踪'!$A$8:$A$20</f>
+              <f>'30日跟踪'!$A$8:$A$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'30日跟踪'!$D$8:$D$20</f>
+              <f>'30日跟踪'!$D$8:$D$21</f>
             </numRef>
           </val>
         </ser>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="7">
@@ -948,6 +948,26 @@
       <c r="E20" t="inlineStr">
         <is>
           <t>第13/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B21" s="4" t="n">
+        <v>13.69999980926514</v>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>-4.927134251666776</v>
+      </c>
+      <c r="D21" s="6">
+        <f>B21/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>第14/30个交易日</t>
         </is>
       </c>
     </row>

--- a/data/CROSS/EXCLE/LUNR_1_20260921.xlsx
+++ b/data/CROSS/EXCLE/LUNR_1_20260921.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'30日跟踪'!$A$8:$A$21</f>
+              <f>'30日跟踪'!$A$8:$A$22</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'30日跟踪'!$D$8:$D$21</f>
+              <f>'30日跟踪'!$D$8:$D$22</f>
             </numRef>
           </val>
         </ser>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="7">
@@ -968,6 +968,26 @@
       <c r="E21" t="inlineStr">
         <is>
           <t>第14/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B22" s="4" t="n">
+        <v>13.1899995803833</v>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>-3.722629459724003</v>
+      </c>
+      <c r="D22" s="6">
+        <f>B22/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>第15/30个交易日</t>
         </is>
       </c>
     </row>

--- a/data/CROSS/EXCLE/LUNR_1_20260921.xlsx
+++ b/data/CROSS/EXCLE/LUNR_1_20260921.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'30日跟踪'!$A$8:$A$22</f>
+              <f>'30日跟踪'!$A$8:$A$23</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'30日跟踪'!$D$8:$D$22</f>
+              <f>'30日跟踪'!$D$8:$D$23</f>
             </numRef>
           </val>
         </ser>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46304</v>
+        <v>46307</v>
       </c>
     </row>
     <row r="7">
@@ -988,6 +988,26 @@
       <c r="E22" t="inlineStr">
         <is>
           <t>第15/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B23" s="4" t="n">
+        <v>12.85999965667725</v>
+      </c>
+      <c r="C23" s="4" t="n">
+        <v>-2.501894876455069</v>
+      </c>
+      <c r="D23" s="6">
+        <f>B23/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>第16/30个交易日</t>
         </is>
       </c>
     </row>

--- a/data/CROSS/EXCLE/LUNR_1_20260921.xlsx
+++ b/data/CROSS/EXCLE/LUNR_1_20260921.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'30日跟踪'!$A$8:$A$23</f>
+              <f>'30日跟踪'!$A$8:$A$24</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'30日跟踪'!$D$8:$D$23</f>
+              <f>'30日跟踪'!$D$8:$D$24</f>
             </numRef>
           </val>
         </ser>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="7">
@@ -1008,6 +1008,26 @@
       <c r="E23" t="inlineStr">
         <is>
           <t>第16/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B24" s="4" t="n">
+        <v>12.18000030517578</v>
+      </c>
+      <c r="C24" s="4" t="n">
+        <v>-5.287708939777391</v>
+      </c>
+      <c r="D24" s="6">
+        <f>B24/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>第17/30个交易日</t>
         </is>
       </c>
     </row>

--- a/data/CROSS/EXCLE/LUNR_1_20260921.xlsx
+++ b/data/CROSS/EXCLE/LUNR_1_20260921.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'30日跟踪'!$A$8:$A$24</f>
+              <f>'30日跟踪'!$A$8:$A$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'30日跟踪'!$D$8:$D$24</f>
+              <f>'30日跟踪'!$D$8:$D$25</f>
             </numRef>
           </val>
         </ser>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="7">
@@ -1028,6 +1028,26 @@
       <c r="E24" t="inlineStr">
         <is>
           <t>第17/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B25" s="4" t="n">
+        <v>11.02000045776367</v>
+      </c>
+      <c r="C25" s="4" t="n">
+        <v>-9.523808032411774</v>
+      </c>
+      <c r="D25" s="6">
+        <f>B25/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>第18/30个交易日</t>
         </is>
       </c>
     </row>

--- a/data/CROSS/EXCLE/LUNR_1_20260921.xlsx
+++ b/data/CROSS/EXCLE/LUNR_1_20260921.xlsx
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="7">

--- a/data/CROSS/EXCLE/LUNR_1_20260921.xlsx
+++ b/data/CROSS/EXCLE/LUNR_1_20260921.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'30日跟踪'!$A$8:$A$25</f>
+              <f>'30日跟踪'!$A$8:$A$27</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'30日跟踪'!$D$8:$D$25</f>
+              <f>'30日跟踪'!$D$8:$D$27</f>
             </numRef>
           </val>
         </ser>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="7">
@@ -1048,6 +1048,46 @@
       <c r="E25" t="inlineStr">
         <is>
           <t>第18/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B26" s="4" t="n">
+        <v>11.56999969482422</v>
+      </c>
+      <c r="C26" s="4" t="n">
+        <v>4.990918459291604</v>
+      </c>
+      <c r="D26" s="6">
+        <f>B26/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>第19/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B27" s="4" t="n">
+        <v>10.77999973297119</v>
+      </c>
+      <c r="C27" s="4" t="n">
+        <v>-6.828003307609675</v>
+      </c>
+      <c r="D27" s="6">
+        <f>B27/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>第20/30个交易日</t>
         </is>
       </c>
     </row>

--- a/data/CROSS/EXCLE/LUNR_1_20260921.xlsx
+++ b/data/CROSS/EXCLE/LUNR_1_20260921.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'30日跟踪'!$A$8:$A$27</f>
+              <f>'30日跟踪'!$A$8:$A$28</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'30日跟踪'!$D$8:$D$27</f>
+              <f>'30日跟踪'!$D$8:$D$28</f>
             </numRef>
           </val>
         </ser>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46311</v>
+        <v>46314</v>
       </c>
     </row>
     <row r="7">
@@ -1088,6 +1088,26 @@
       <c r="E27" t="inlineStr">
         <is>
           <t>第20/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B28" s="4" t="n">
+        <v>10.73999977111816</v>
+      </c>
+      <c r="C28" s="4" t="n">
+        <v>-0.3710571692380094</v>
+      </c>
+      <c r="D28" s="6">
+        <f>B28/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>第21/30个交易日</t>
         </is>
       </c>
     </row>

--- a/data/CROSS/EXCLE/LUNR_1_20260921.xlsx
+++ b/data/CROSS/EXCLE/LUNR_1_20260921.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'30日跟踪'!$A$8:$A$28</f>
+              <f>'30日跟踪'!$A$8:$A$29</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'30日跟踪'!$D$8:$D$28</f>
+              <f>'30日跟踪'!$D$8:$D$29</f>
             </numRef>
           </val>
         </ser>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
     </row>
     <row r="7">
@@ -1108,6 +1108,26 @@
       <c r="E28" t="inlineStr">
         <is>
           <t>第21/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B29" s="4" t="n">
+        <v>10.53999996185303</v>
+      </c>
+      <c r="C29" s="4" t="n">
+        <v>-1.862195656679366</v>
+      </c>
+      <c r="D29" s="6">
+        <f>B29/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>第22/30个交易日</t>
         </is>
       </c>
     </row>

--- a/data/CROSS/EXCLE/LUNR_1_20260921.xlsx
+++ b/data/CROSS/EXCLE/LUNR_1_20260921.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'30日跟踪'!$A$8:$A$29</f>
+              <f>'30日跟踪'!$A$8:$A$30</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'30日跟踪'!$D$8:$D$29</f>
+              <f>'30日跟踪'!$D$8:$D$30</f>
             </numRef>
           </val>
         </ser>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
     </row>
     <row r="7">
@@ -1128,6 +1128,26 @@
       <c r="E29" t="inlineStr">
         <is>
           <t>第22/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B30" s="4" t="n">
+        <v>10.90999984741211</v>
+      </c>
+      <c r="C30" s="4" t="n">
+        <v>3.510435359565522</v>
+      </c>
+      <c r="D30" s="6">
+        <f>B30/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>第23/30个交易日</t>
         </is>
       </c>
     </row>

--- a/data/CROSS/EXCLE/LUNR_1_20260921.xlsx
+++ b/data/CROSS/EXCLE/LUNR_1_20260921.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'30日跟踪'!$A$8:$A$30</f>
+              <f>'30日跟踪'!$A$8:$A$31</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'30日跟踪'!$D$8:$D$30</f>
+              <f>'30日跟踪'!$D$8:$D$31</f>
             </numRef>
           </val>
         </ser>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
     </row>
     <row r="7">
@@ -1148,6 +1148,26 @@
       <c r="E30" t="inlineStr">
         <is>
           <t>第23/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B31" s="4" t="n">
+        <v>10.44999980926514</v>
+      </c>
+      <c r="C31" s="4" t="n">
+        <v>-4.21631571567882</v>
+      </c>
+      <c r="D31" s="6">
+        <f>B31/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>第24/30个交易日</t>
         </is>
       </c>
     </row>

--- a/data/CROSS/EXCLE/LUNR_1_20260921.xlsx
+++ b/data/CROSS/EXCLE/LUNR_1_20260921.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'30日跟踪'!$A$8:$A$31</f>
+              <f>'30日跟踪'!$A$8:$A$32</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'30日跟踪'!$D$8:$D$31</f>
+              <f>'30日跟踪'!$D$8:$D$32</f>
             </numRef>
           </val>
         </ser>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
     </row>
     <row r="7">
@@ -1168,6 +1168,26 @@
       <c r="E31" t="inlineStr">
         <is>
           <t>第24/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B32" s="4" t="n">
+        <v>10.52000045776367</v>
+      </c>
+      <c r="C32" s="4" t="n">
+        <v>0.669862677284172</v>
+      </c>
+      <c r="D32" s="6">
+        <f>B32/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>第25/30个交易日</t>
         </is>
       </c>
     </row>

--- a/data/CROSS/EXCLE/LUNR_1_20260921.xlsx
+++ b/data/CROSS/EXCLE/LUNR_1_20260921.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'30日跟踪'!$A$8:$A$32</f>
+              <f>'30日跟踪'!$A$8:$A$33</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'30日跟踪'!$D$8:$D$32</f>
+              <f>'30日跟踪'!$D$8:$D$33</f>
             </numRef>
           </val>
         </ser>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46318</v>
+        <v>46321</v>
       </c>
     </row>
     <row r="7">
@@ -1188,6 +1188,26 @@
       <c r="E32" t="inlineStr">
         <is>
           <t>第25/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B33" s="4" t="n">
+        <v>10.47999954223633</v>
+      </c>
+      <c r="C33" s="4" t="n">
+        <v>-0.3802368230680364</v>
+      </c>
+      <c r="D33" s="6">
+        <f>B33/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>第26/30个交易日</t>
         </is>
       </c>
     </row>

--- a/data/CROSS/EXCLE/LUNR_1_20260921.xlsx
+++ b/data/CROSS/EXCLE/LUNR_1_20260921.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'30日跟踪'!$A$8:$A$33</f>
+              <f>'30日跟踪'!$A$8:$A$34</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'30日跟踪'!$D$8:$D$33</f>
+              <f>'30日跟踪'!$D$8:$D$34</f>
             </numRef>
           </val>
         </ser>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
     </row>
     <row r="7">
@@ -1208,6 +1208,26 @@
       <c r="E33" t="inlineStr">
         <is>
           <t>第26/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B34" s="4" t="n">
+        <v>11.5600004196167</v>
+      </c>
+      <c r="C34" s="4" t="n">
+        <v>10.3053523335356</v>
+      </c>
+      <c r="D34" s="6">
+        <f>B34/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>第27/30个交易日</t>
         </is>
       </c>
     </row>

--- a/data/CROSS/EXCLE/LUNR_1_20260921.xlsx
+++ b/data/CROSS/EXCLE/LUNR_1_20260921.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'30日跟踪'!$A$8:$A$34</f>
+              <f>'30日跟踪'!$A$8:$A$35</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'30日跟踪'!$D$8:$D$34</f>
+              <f>'30日跟踪'!$D$8:$D$35</f>
             </numRef>
           </val>
         </ser>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
     </row>
     <row r="7">
@@ -1228,6 +1228,26 @@
       <c r="E34" t="inlineStr">
         <is>
           <t>第27/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B35" s="4" t="n">
+        <v>11.59000015258789</v>
+      </c>
+      <c r="C35" s="4" t="n">
+        <v>0.2595132515763821</v>
+      </c>
+      <c r="D35" s="6">
+        <f>B35/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>第28/30个交易日</t>
         </is>
       </c>
     </row>

--- a/data/CROSS/EXCLE/LUNR_1_20260921.xlsx
+++ b/data/CROSS/EXCLE/LUNR_1_20260921.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'30日跟踪'!$A$8:$A$35</f>
+              <f>'30日跟踪'!$A$8:$A$36</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'30日跟踪'!$D$8:$D$35</f>
+              <f>'30日跟踪'!$D$8:$D$36</f>
             </numRef>
           </val>
         </ser>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E35"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
     </row>
     <row r="7">
@@ -1248,6 +1248,26 @@
       <c r="E35" t="inlineStr">
         <is>
           <t>第28/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B36" s="4" t="n">
+        <v>11.68000030517578</v>
+      </c>
+      <c r="C36" s="4" t="n">
+        <v>0.7765327989904813</v>
+      </c>
+      <c r="D36" s="6">
+        <f>B36/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>第29/30个交易日</t>
         </is>
       </c>
     </row>
